--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:29:13+00:00</t>
+    <t>2026-09-03T10:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,31 +78,34 @@
     <t>Jurisdiction</t>
   </si>
   <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet für NARSE-spezifische Therapietypen bei Seltenen Erkrankungen</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ValueSet für NARSE-spezifische Therapietypen bei Seltenen Erkrankungen</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
@@ -391,18 +394,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-narse-therapietyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
